--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_61_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_61_IN_Piura.xlsx
@@ -1797,7 +1797,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>46.03</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="C11" s="30">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>32.88</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>20.29</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.81</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1914,11 +1914,11 @@
       </c>
       <c r="B15" s="43">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>26.8256</v>
       </c>
       <c r="C15" s="44">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.01</v>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
@@ -1939,11 +1939,11 @@
       </c>
       <c r="B16" s="46">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>21.166</v>
       </c>
       <c r="C16" s="47">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>78.9</v>
       </c>
       <c r="D16" s="45" t="inlineStr">
         <is>
@@ -1964,11 +1964,11 @@
       </c>
       <c r="B17" s="46">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>5.6596</v>
       </c>
       <c r="C17" s="47">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>21.1</v>
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
@@ -2124,11 +2124,11 @@
       </c>
       <c r="B27" s="22">
         <f>SUM(B25:B26)</f>
-        <v/>
+        <v>26.8329</v>
       </c>
       <c r="C27" s="23">
         <f>SUM(C25:C26)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
       <c r="E27" s="17" t="inlineStr"/>
@@ -2247,6 +2247,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2331,6 +2332,7 @@
       <c r="F11" s="17" t="inlineStr"/>
       <c r="G11" s="17" t="inlineStr"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -2375,6 +2377,7 @@
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16" ht="180" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
@@ -2697,11 +2700,11 @@
       </c>
       <c r="B15" s="32">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>148.43</v>
       </c>
       <c r="C15" s="23">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.01</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -2711,19 +2714,19 @@
       <c r="E15" s="17" t="inlineStr"/>
       <c r="F15" s="17">
         <f>ROUND(AVERAGE(F10:F14),2)</f>
-        <v/>
+        <v>28.14</v>
       </c>
       <c r="G15" s="22">
         <f>ROUND(AVERAGE(G10:G14),4)</f>
-        <v/>
+        <v>0.667</v>
       </c>
       <c r="H15" s="23">
         <f>ROUND(AVERAGE(H10:H14),2)</f>
-        <v/>
+        <v>94.61</v>
       </c>
       <c r="I15" s="23">
         <f>ROUND(AVERAGE(I10:I14),2)</f>
-        <v/>
+        <v>5.51</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1">
